--- a/docs/files/2026-10-01/상담행정공고_2026-10-01.xlsx
+++ b/docs/files/2026-10-01/상담행정공고_2026-10-01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="공고" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공고" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$13</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'공고'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -589,14 +589,14 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1064131</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1064117</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>상담</t>
+          <t>상담 · 청소년 · 복지</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -606,22 +606,22 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>성모자애드림힐</t>
+          <t>도봉구청소년상담복지센터</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>성모자애드림힐 임상심리사 채용 재공고</t>
+          <t>2026년도봉구청소년상담복지센터팀원(청소년안전망) 채용 재공고</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 노원구</t>
+          <t>서울특별시 도봉구</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
@@ -632,17 +632,17 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>오늘</t>
+          <t>D-2</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr"/>
@@ -654,14 +654,14 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1064117</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068986</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년 · 복지</t>
+          <t>상담</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -671,22 +671,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>도봉구청소년상담복지센터</t>
+          <t>성모자애드림힐</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2026년도봉구청소년상담복지센터팀원(청소년안전망) 채용 재공고</t>
+          <t>성모자애드림힐 임상심리사 채용 재공고</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 도봉구</t>
+          <t>서울특별시 노원구</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
@@ -697,17 +697,17 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-14</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr"/>
@@ -719,7 +719,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068986</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1064131</t>
         </is>
       </c>
     </row>
@@ -994,28 +994,28 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년</t>
+          <t>청소년 · 복지</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>강동여자단기청소년쉼터</t>
+          <t>우천복지재단</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>강동여자단기청소년쉼터 직원채용(보호상담원)</t>
+          <t>탈북청소년 런페어 진로사례관리사업 담당자</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 강동구</t>
+          <t>서울특별시 금천구</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
@@ -1026,17 +1026,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>D-16</t>
+          <t>D-15</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr"/>
@@ -1048,56 +1048,56 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069566</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070432</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>상담</t>
+          <t>상담 · 청소년</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>굿네이버스 경원본부 아주좋은이웃심리치유센터</t>
+          <t>강동여자단기청소년쉼터</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>굿네이버스 경기지부 아주좋은이웃심리치유센터 놀이치료사 모집</t>
+          <t>강동여자단기청소년쉼터 직원채용(보호상담원)</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>경기도 수원시</t>
+          <t>서울특별시 강동구</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>오늘</t>
+          <t>D-16</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr"/>
@@ -1109,25 +1109,25 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068302</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069566</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년 · 복지 · 교육</t>
+          <t>상담</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>용인시처인장애인복지관</t>
+          <t>굿네이버스 경원본부 아주좋은이웃심리치유센터</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>용인시처인장애인복지관 장애아동발달재활사업 미술심리재활강사 모집 공고</t>
+          <t>굿네이버스 경기지부 아주좋은이웃심리치유센터 놀이치료사 모집</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1137,28 +1137,28 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>경기도</t>
+          <t>경기도 수원시</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>오늘</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr"/>
@@ -1170,12 +1170,138 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068302</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 청소년 · 복지 · 교육</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr"/>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>용인시처인장애인복지관</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>용인시처인장애인복지관 장애아동발달재활사업 미술심리재활강사 모집 공고</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>경기도</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>D-4</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
           <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068718</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 청소년</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>오산시아동보호전문기관</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>오산시아동보호전문기관 프리랜서 심리치료사, 임상심리사 채용</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>파트타임</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>경기도 오산시</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>D-8</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070359</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O11"/>
+  <autoFilter ref="A1:O13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/docs/files/2026-10-01/상담행정공고_2026-10-01.xlsx
+++ b/docs/files/2026-10-01/상담행정공고_2026-10-01.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공고" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$17</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'공고'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -933,28 +933,28 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>상담 · 복지</t>
+          <t>청소년 · 복지</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>양천해누리복지관</t>
+          <t>사회복지법인 생명의전화</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>[양천해누리복지관] 심리운동사 채용공고(건강누리팀)</t>
+          <t>[채용공고]사회복지법인 생명의전화 직원채용(청소년사업팀)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 양천구</t>
+          <t>서울특별시</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
@@ -965,17 +965,17 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>D-15</t>
+          <t>D-14</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr"/>
@@ -987,35 +987,35 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1066336</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070875</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 복지</t>
+          <t>상담 · 복지</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>우천복지재단</t>
+          <t>양천해누리복지관</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>탈북청소년 런페어 진로사례관리사업 담당자</t>
+          <t>[양천해누리복지관] 심리운동사 채용공고(건강누리팀)</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 금천구</t>
+          <t>서울특별시 양천구</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1048,35 +1048,35 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070432</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1066336</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년</t>
+          <t>청소년 · 복지</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>강동여자단기청소년쉼터</t>
+          <t>우천복지재단</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>강동여자단기청소년쉼터 직원채용(보호상담원)</t>
+          <t>탈북청소년 런페어 진로사례관리사업 담당자</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 강동구</t>
+          <t>서울특별시 금천구</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
@@ -1087,17 +1087,17 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>D-16</t>
+          <t>D-15</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr"/>
@@ -1109,56 +1109,56 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069566</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070432</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>상담</t>
+          <t>상담 · 청소년</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>굿네이버스 경원본부 아주좋은이웃심리치유센터</t>
+          <t>강동여자단기청소년쉼터</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>굿네이버스 경기지부 아주좋은이웃심리치유센터 놀이치료사 모집</t>
+          <t>강동여자단기청소년쉼터 직원채용(보호상담원)</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>경기도 수원시</t>
+          <t>서울특별시 강동구</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>오늘</t>
+          <t>D-16</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr"/>
@@ -1170,25 +1170,25 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068302</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069566</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년 · 복지 · 교육</t>
+          <t>상담</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>용인시처인장애인복지관</t>
+          <t>굿네이버스 경원본부 아주좋은이웃심리치유센터</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>용인시처인장애인복지관 장애아동발달재활사업 미술심리재활강사 모집 공고</t>
+          <t>굿네이버스 경기지부 아주좋은이웃심리치유센터 놀이치료사 모집</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1198,28 +1198,28 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>경기도</t>
+          <t>경기도 수원시</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>오늘</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr"/>
@@ -1231,60 +1231,56 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068718</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068302</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+          <t>상담 · 청소년 · 복지 · 교육</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>오산시아동보호전문기관</t>
+          <t>용인시처인장애인복지관</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>오산시아동보호전문기관 프리랜서 심리치료사, 임상심리사 채용</t>
+          <t>용인시처인장애인복지관 장애아동발달재활사업 미술심리재활강사 모집 공고</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>파트타임</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>경기도 오산시</t>
+          <t>경기도</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-4</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr"/>
@@ -1296,12 +1292,260 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068718</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 청소년</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>오산시아동보호전문기관</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>오산시아동보호전문기관 프리랜서 심리치료사, 임상심리사 채용</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>파트타임</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>경기도 오산시</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>D-8</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
           <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070359</t>
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>상담</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr"/>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>대전해바라기센터</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>대전해바라기센터 상담원(단기간계약직) 모집 공고</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>대전광역시 중구</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>D-4</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069214</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 복지</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr"/>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>(사)대전지체장애인협회 중구지회</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>사회복지사 상담사 긴급 모집</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>정규직</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>대전광역시 중구</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>D-5</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069573</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 청소년</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr"/>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>솔이랑</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>든솔 사회적협동조합 대전지부 학대피해아동쉼터 직원(심리치료사) 채용 공고</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>대전광역시 중구</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>D-15</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068844</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O13"/>
+  <autoFilter ref="A1:O17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/docs/files/2026-10-01/상담행정공고_2026-10-01.xlsx
+++ b/docs/files/2026-10-01/상담행정공고_2026-10-01.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>정규직,무기계약직,비정규직,청년인턴(체험형)</t>
+          <t>정규직 · 무기직 · 체험형 인턴 · 계약직 · 대체인력</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>비정규직</t>
+          <t>계약직 · 대체인력</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>파트타임</t>
+          <t>시간제</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
